--- a/data/kz/niches/niche_formats_PVZ.xlsx
+++ b/data/kz/niches/niche_formats_PVZ.xlsx
@@ -502,6 +502,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -590,12 +591,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -645,12 +646,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>PVZ_MULTI</t>
+          <t>PVZ_STANDARD</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -725,6 +726,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -780,12 +782,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -854,6 +856,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -904,12 +907,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -937,12 +940,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1005,6 +1008,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1104,6 +1108,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1418,6 +1423,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1524,6 +1530,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1604,12 +1611,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1663,12 +1670,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PVZ_MULTI</t>
+          <t>PVZ_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1768,6 +1775,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1888,12 +1896,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -1963,12 +1971,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PVZ_MULTI</t>
+          <t>PVZ_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2074,6 +2082,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2144,12 +2153,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2191,12 +2200,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PVZ_MULTI</t>
+          <t>PVZ_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2270,6 +2279,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2340,12 +2350,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2385,12 +2395,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PVZ_MULTI</t>
+          <t>PVZ_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2463,6 +2473,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2518,12 +2529,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2560,12 +2571,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PVZ_MULTI</t>
+          <t>PVZ_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2638,6 +2649,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2708,12 +2720,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2769,12 +2781,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PVZ_MULTI</t>
+          <t>PVZ_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2861,6 +2873,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2906,12 +2919,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2940,12 +2953,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2974,12 +2987,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -3008,12 +3021,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -3069,6 +3082,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3094,12 +3108,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3116,12 +3130,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
